--- a/artfynd/S 6436-2022 artfynd.xlsx
+++ b/artfynd/S 6436-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY153"/>
+  <dimension ref="A1:AZ153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96195902</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99596627</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97204276</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1091,6 +1111,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99596565</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203951</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1305,6 +1335,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99590846</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1411,6 +1446,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99596274</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1517,6 +1557,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99596526</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1615,6 +1660,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106662316</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1726,6 +1776,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75026227</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1837,6 +1892,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75026231</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1948,6 +2008,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93746642</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2050,6 +2115,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93746786</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2152,6 +2222,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96064111</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2261,6 +2336,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96094943</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2362,6 +2442,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96064202</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2463,6 +2548,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96064208</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2564,6 +2654,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96095001</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2665,6 +2760,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96095008</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2766,6 +2866,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96095049</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2871,6 +2976,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97190954</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2977,6 +3087,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97191115</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3078,6 +3193,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99596285</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3187,6 +3307,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89613829</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3296,6 +3421,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93677310</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3409,6 +3539,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97190891</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3523,6 +3658,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97190920</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3632,6 +3772,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96064212</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3741,6 +3886,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96094998</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3850,6 +4000,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96095005</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3959,6 +4114,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96095013</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4068,6 +4228,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96095018</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4177,6 +4342,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96095046</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4278,6 +4448,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96248560</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4379,6 +4554,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96248587</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4480,6 +4660,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96248600</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4581,6 +4766,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96248618</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4682,6 +4872,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96263085</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4783,6 +4978,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96263089</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4880,6 +5080,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119669612</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4995,6 +5200,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90745715</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5109,6 +5319,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203790</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5233,6 +5448,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90685328</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5356,6 +5576,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98521459</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5475,6 +5700,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90685333</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5583,6 +5813,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99596262</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5690,6 +5925,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101542424</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5805,6 +6045,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91488263</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5910,6 +6155,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90431090</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6024,6 +6274,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97191028</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6138,6 +6393,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97204179</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6246,6 +6506,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101866127</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6357,6 +6622,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93677307</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6459,6 +6729,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96064128</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6561,6 +6836,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96095028</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6663,6 +6943,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96095059</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6777,6 +7062,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97190488</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6891,6 +7181,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97190515</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7005,6 +7300,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97190526</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7119,6 +7419,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97190542</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7233,6 +7538,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97190547</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7347,6 +7657,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97190761</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7461,6 +7776,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97190764</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7575,6 +7895,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97190800</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7689,6 +8014,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97190809</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7803,6 +8133,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97190818</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7917,6 +8252,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97190822</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8031,6 +8371,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97190832</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8145,6 +8490,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97190837</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8259,6 +8609,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97190850</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8373,6 +8728,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97190869</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8487,6 +8847,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97190882</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8601,6 +8966,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97190885</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8715,6 +9085,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97190922</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8829,6 +9204,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97190923</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8943,6 +9323,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97190924</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9057,6 +9442,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97190947</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9171,6 +9561,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97190958</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9285,6 +9680,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97190962</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9399,6 +9799,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97190965</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9513,6 +9918,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97190969</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9627,6 +10037,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97190978</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9741,6 +10156,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97190981</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9855,6 +10275,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97190984</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9969,6 +10394,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97190989</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10083,6 +10513,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97190992</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10197,6 +10632,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97190999</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10311,6 +10751,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97191005</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10425,6 +10870,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97191015</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10540,6 +10990,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97191024</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10655,6 +11110,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97191044</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10770,6 +11230,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97191072</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10885,6 +11350,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97191083</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11000,6 +11470,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97191094</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11115,6 +11590,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97191095</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11230,6 +11710,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97191097</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11345,6 +11830,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97191100</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11460,6 +11950,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97191114</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11575,6 +12070,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97191126</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11690,6 +12190,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97191132</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11805,6 +12310,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203640</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11920,6 +12430,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203731</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12035,6 +12550,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203764</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12150,6 +12670,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203769</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12265,6 +12790,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203773</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12380,6 +12910,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203786</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12495,6 +13030,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203801</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12610,6 +13150,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203811</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12725,6 +13270,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203824</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12840,6 +13390,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203838</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12955,6 +13510,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203845</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13070,6 +13630,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203852</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13185,6 +13750,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203865</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13300,6 +13870,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203874</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13415,6 +13990,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203882</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13530,6 +14110,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203887</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13645,6 +14230,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203891</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13760,6 +14350,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203907</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13874,6 +14469,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203910</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13988,6 +14588,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203916</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14102,6 +14707,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203921</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14216,6 +14826,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203927</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14330,6 +14945,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203930</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14444,6 +15064,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203935</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14558,6 +15183,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203942</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14672,6 +15302,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203956</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14786,6 +15421,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203962</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14901,6 +15541,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203967</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15016,6 +15661,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203976</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15131,6 +15781,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203983</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15246,6 +15901,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203992</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15361,6 +16021,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97204004</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15476,6 +16141,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97204011</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15591,6 +16261,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97204019</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15706,6 +16381,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97204026</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15821,6 +16501,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97204135</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15936,6 +16621,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97204168</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -16051,6 +16741,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97204172</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16166,6 +16861,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97204175</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16281,6 +16981,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97204187</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16396,6 +17101,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97204195</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16511,6 +17221,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97204199</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16626,6 +17341,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97204205</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16741,6 +17461,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97204206</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16856,6 +17581,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97204223</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -16971,6 +17701,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97204234</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -17081,6 +17816,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99582159</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -17178,6 +17918,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119669616</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -17292,6 +18037,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93823545</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -17401,6 +18151,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96649976</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17510,6 +18265,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96649997</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17621,8 +18381,167 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203603</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>